--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/84.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/84.xlsx
@@ -426,13 +426,13 @@
         <v>-5.099270441692573</v>
       </c>
       <c r="E2">
-        <v>-8.274088427822189</v>
+        <v>-11.29657135662086</v>
       </c>
       <c r="F2">
-        <v>-3.169647781604077</v>
+        <v>-3.177014452917173</v>
       </c>
       <c r="G2">
-        <v>-9.444592538218064</v>
+        <v>-10.47808450280076</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-5.078385059032422</v>
       </c>
       <c r="E3">
-        <v>-9.049243789488189</v>
+        <v>-11.82959865126068</v>
       </c>
       <c r="F3">
-        <v>-3.758395002530575</v>
+        <v>-3.047914221558273</v>
       </c>
       <c r="G3">
-        <v>-9.806714561356138</v>
+        <v>-10.21348553849143</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-5.079060210860995</v>
       </c>
       <c r="E4">
-        <v>-11.19111716787214</v>
+        <v>-12.88718068943767</v>
       </c>
       <c r="F4">
-        <v>-3.029732385434227</v>
+        <v>-2.830926693864554</v>
       </c>
       <c r="G4">
-        <v>-9.106455425638549</v>
+        <v>-9.654111318516383</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-5.093978585610262</v>
       </c>
       <c r="E5">
-        <v>-10.50545520383355</v>
+        <v>-12.45111011317597</v>
       </c>
       <c r="F5">
-        <v>-2.850504329062317</v>
+        <v>-2.903031106073834</v>
       </c>
       <c r="G5">
-        <v>-8.900979383339569</v>
+        <v>-9.225205143365336</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-5.122288558368078</v>
       </c>
       <c r="E6">
-        <v>-11.97266016855573</v>
+        <v>-13.63839278781603</v>
       </c>
       <c r="F6">
-        <v>-2.852145324887263</v>
+        <v>-2.971755779279692</v>
       </c>
       <c r="G6">
-        <v>-9.193374945310484</v>
+        <v>-8.925927658652247</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.148355855833563</v>
       </c>
       <c r="E7">
-        <v>-12.85427064289973</v>
+        <v>-14.38040967632123</v>
       </c>
       <c r="F7">
-        <v>-3.290600191189041</v>
+        <v>-2.65573030164207</v>
       </c>
       <c r="G7">
-        <v>-7.468455993961936</v>
+        <v>-9.144430011088588</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.15773030124095</v>
       </c>
       <c r="E8">
-        <v>-11.81733006500714</v>
+        <v>-15.24147006102998</v>
       </c>
       <c r="F8">
-        <v>-2.864545156539769</v>
+        <v>-2.691242412200084</v>
       </c>
       <c r="G8">
-        <v>-7.39626107378388</v>
+        <v>-8.400314282357183</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.117633658773483</v>
       </c>
       <c r="E9">
-        <v>-13.06215963576402</v>
+        <v>-16.11796377902179</v>
       </c>
       <c r="F9">
-        <v>-2.394710904652543</v>
+        <v>-2.954266458304386</v>
       </c>
       <c r="G9">
-        <v>-7.020689799884687</v>
+        <v>-7.9486802701682</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.996270018173447</v>
       </c>
       <c r="E10">
-        <v>-15.10598815440275</v>
+        <v>-17.56197721170613</v>
       </c>
       <c r="F10">
-        <v>-2.55556908549997</v>
+        <v>-2.791923843071142</v>
       </c>
       <c r="G10">
-        <v>-6.841639714336957</v>
+        <v>-7.840942673126729</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.754650455583282</v>
       </c>
       <c r="E11">
-        <v>-14.20107401131513</v>
+        <v>-17.6789980939945</v>
       </c>
       <c r="F11">
-        <v>-2.424810462600665</v>
+        <v>-2.413740988997056</v>
       </c>
       <c r="G11">
-        <v>-6.027539060723874</v>
+        <v>-6.866058008497639</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.370686311376215</v>
       </c>
       <c r="E12">
-        <v>-17.23297227018719</v>
+        <v>-17.94313818104227</v>
       </c>
       <c r="F12">
-        <v>-2.468162242258775</v>
+        <v>-2.709877365293462</v>
       </c>
       <c r="G12">
-        <v>-4.646517829895132</v>
+        <v>-6.31782775180976</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.833425228527386</v>
       </c>
       <c r="E13">
-        <v>-18.01799566196098</v>
+        <v>-19.49276362450567</v>
       </c>
       <c r="F13">
-        <v>-2.841113127816779</v>
+        <v>-2.162818562280252</v>
       </c>
       <c r="G13">
-        <v>-5.713839822889475</v>
+        <v>-6.56809372831388</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.161882559703221</v>
       </c>
       <c r="E14">
-        <v>-18.77645926731249</v>
+        <v>-20.79776492093667</v>
       </c>
       <c r="F14">
-        <v>-1.971472319172788</v>
+        <v>-2.540642733268926</v>
       </c>
       <c r="G14">
-        <v>-4.389787649783417</v>
+        <v>-5.550138304792898</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.387930165701862</v>
       </c>
       <c r="E15">
-        <v>-21.02628291445139</v>
+        <v>-22.00564752374788</v>
       </c>
       <c r="F15">
-        <v>-1.987058880223864</v>
+        <v>-2.328971667566374</v>
       </c>
       <c r="G15">
-        <v>-4.142960023905792</v>
+        <v>-4.760557764379552</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.562980086008473</v>
       </c>
       <c r="E16">
-        <v>-19.62055793697064</v>
+        <v>-23.16052684363163</v>
       </c>
       <c r="F16">
-        <v>-1.632919390016033</v>
+        <v>-2.284970447864469</v>
       </c>
       <c r="G16">
-        <v>-3.501797702752645</v>
+        <v>-4.918930752765666</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.7345910517029498</v>
       </c>
       <c r="E17">
-        <v>-19.22817083742349</v>
+        <v>-22.80253664027671</v>
       </c>
       <c r="F17">
-        <v>-2.665123987989816</v>
+        <v>-2.007116968515251</v>
       </c>
       <c r="G17">
-        <v>-3.721865196571358</v>
+        <v>-4.17175131525659</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.04380703414037543</v>
       </c>
       <c r="E18">
-        <v>-21.30297815933411</v>
+        <v>-24.68194367577679</v>
       </c>
       <c r="F18">
-        <v>-2.705559914390071</v>
+        <v>-2.099267043504876</v>
       </c>
       <c r="G18">
-        <v>-3.352536212989517</v>
+        <v>-4.007921870675049</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.7330217406853089</v>
       </c>
       <c r="E19">
-        <v>-22.47502270162338</v>
+        <v>-25.7391103928213</v>
       </c>
       <c r="F19">
-        <v>-1.531148656010294</v>
+        <v>-2.279813860782043</v>
       </c>
       <c r="G19">
-        <v>-2.099026358735339</v>
+        <v>-3.566238711495095</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.293355745955919</v>
       </c>
       <c r="E20">
-        <v>-25.71818651416681</v>
+        <v>-26.34193240377487</v>
       </c>
       <c r="F20">
-        <v>-1.355383175382087</v>
+        <v>-1.684573896152402</v>
       </c>
       <c r="G20">
-        <v>-3.565353669078707</v>
+        <v>-3.043612027012264</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.703513767697034</v>
       </c>
       <c r="E21">
-        <v>-23.81699173205668</v>
+        <v>-27.27305331032215</v>
       </c>
       <c r="F21">
-        <v>-1.843743035865521</v>
+        <v>-1.651536947393952</v>
       </c>
       <c r="G21">
-        <v>-2.007577197197823</v>
+        <v>-3.439113725120015</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.944183182671513</v>
       </c>
       <c r="E22">
-        <v>-25.89269614761346</v>
+        <v>-27.39821864001851</v>
       </c>
       <c r="F22">
-        <v>-1.562494078532228</v>
+        <v>-1.586035451752387</v>
       </c>
       <c r="G22">
-        <v>-2.333499941207815</v>
+        <v>-2.664850423222731</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.014825418720441</v>
       </c>
       <c r="E23">
-        <v>-25.36434121571407</v>
+        <v>-27.98251317525201</v>
       </c>
       <c r="F23">
-        <v>-1.220492655877618</v>
+        <v>-1.123186822172969</v>
       </c>
       <c r="G23">
-        <v>-1.562257270802448</v>
+        <v>-2.828082007292906</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.917257918047145</v>
       </c>
       <c r="E24">
-        <v>-26.01976364809659</v>
+        <v>-28.71737408064452</v>
       </c>
       <c r="F24">
-        <v>-1.643631008901633</v>
+        <v>-1.598533859125826</v>
       </c>
       <c r="G24">
-        <v>-2.07714831906181</v>
+        <v>-2.436287566504536</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.669554224047133</v>
       </c>
       <c r="E25">
-        <v>-28.18753437569651</v>
+        <v>-29.72668126698737</v>
       </c>
       <c r="F25">
-        <v>-1.573295989464733</v>
+        <v>-1.330002826527713</v>
       </c>
       <c r="G25">
-        <v>-1.41412362270268</v>
+        <v>-2.24388352237326</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.292317675488139</v>
       </c>
       <c r="E26">
-        <v>-26.16052013310635</v>
+        <v>-28.88835763767639</v>
       </c>
       <c r="F26">
-        <v>-1.592777534043772</v>
+        <v>-1.429751515703218</v>
       </c>
       <c r="G26">
-        <v>-1.688533765185415</v>
+        <v>-2.499485860821615</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.8168840626512777</v>
       </c>
       <c r="E27">
-        <v>-27.68155486980963</v>
+        <v>-29.49077471052578</v>
       </c>
       <c r="F27">
-        <v>-0.9743242296854806</v>
+        <v>-1.290574194889262</v>
       </c>
       <c r="G27">
-        <v>-2.869958350534364</v>
+        <v>-3.029307757397554</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.2751183734033194</v>
       </c>
       <c r="E28">
-        <v>-26.59186020166907</v>
+        <v>-29.94910649948856</v>
       </c>
       <c r="F28">
-        <v>-0.8891117316943011</v>
+        <v>-1.319422918059157</v>
       </c>
       <c r="G28">
-        <v>-2.034423483828241</v>
+        <v>-2.416195276131328</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.2980776302314531</v>
       </c>
       <c r="E29">
-        <v>-27.48376648688733</v>
+        <v>-28.93989068379486</v>
       </c>
       <c r="F29">
-        <v>-0.8304351550844009</v>
+        <v>-1.21173184222561</v>
       </c>
       <c r="G29">
-        <v>-0.6201961925451297</v>
+        <v>-2.488779197253459</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-0.8696443741255528</v>
       </c>
       <c r="E30">
-        <v>-26.85497444551961</v>
+        <v>-28.46969109347139</v>
       </c>
       <c r="F30">
-        <v>-1.655752509106799</v>
+        <v>-1.465284335446303</v>
       </c>
       <c r="G30">
-        <v>-2.247844021917979</v>
+        <v>-2.873950179014176</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.411324178359493</v>
       </c>
       <c r="E31">
-        <v>-27.3390353786397</v>
+        <v>-29.1046215811772</v>
       </c>
       <c r="F31">
-        <v>-1.442360924308632</v>
+        <v>-1.450073853196098</v>
       </c>
       <c r="G31">
-        <v>-2.801512459589147</v>
+        <v>-2.829726776385308</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.89954598322013</v>
       </c>
       <c r="E32">
-        <v>-26.34596517197127</v>
+        <v>-27.75978060511278</v>
       </c>
       <c r="F32">
-        <v>-1.915722364596979</v>
+        <v>-1.341190756669923</v>
       </c>
       <c r="G32">
-        <v>-2.437436294124625</v>
+        <v>-2.937239849391944</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.320847192749249</v>
       </c>
       <c r="E33">
-        <v>-25.44623423661704</v>
+        <v>-28.52822645388352</v>
       </c>
       <c r="F33">
-        <v>-1.629520598562347</v>
+        <v>-1.414771319590992</v>
       </c>
       <c r="G33">
-        <v>-2.575944126916959</v>
+        <v>-3.445935600736595</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.667499881585869</v>
       </c>
       <c r="E34">
-        <v>-24.32044400885239</v>
+        <v>-27.24872795159263</v>
       </c>
       <c r="F34">
-        <v>-1.221323508382626</v>
+        <v>-1.413014352329654</v>
       </c>
       <c r="G34">
-        <v>-3.393501406368675</v>
+        <v>-3.561539371231091</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.942812352403551</v>
       </c>
       <c r="E35">
-        <v>-24.2615805447456</v>
+        <v>-26.89406862372022</v>
       </c>
       <c r="F35">
-        <v>-1.339798271065817</v>
+        <v>-1.252251433733548</v>
       </c>
       <c r="G35">
-        <v>-2.020158375382398</v>
+        <v>-3.117156702143925</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-3.153715398098741</v>
       </c>
       <c r="E36">
-        <v>-25.12416515801056</v>
+        <v>-25.52235014056717</v>
       </c>
       <c r="F36">
-        <v>-1.076851263129975</v>
+        <v>-1.354010570595648</v>
       </c>
       <c r="G36">
-        <v>-1.721389985864576</v>
+        <v>-3.572862170522749</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.314411234997896</v>
       </c>
       <c r="E37">
-        <v>-22.4302303174851</v>
+        <v>-25.91443820889894</v>
       </c>
       <c r="F37">
-        <v>-1.053016647849225</v>
+        <v>-1.274483158089881</v>
       </c>
       <c r="G37">
-        <v>-2.165070364656732</v>
+        <v>-3.605627015141221</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.438930250989823</v>
       </c>
       <c r="E38">
-        <v>-21.71913408729326</v>
+        <v>-24.19366307995068</v>
       </c>
       <c r="F38">
-        <v>-1.352110295773626</v>
+        <v>-1.261585477628293</v>
       </c>
       <c r="G38">
-        <v>-2.134887546438871</v>
+        <v>-3.944436394452948</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.543936771191371</v>
       </c>
       <c r="E39">
-        <v>-22.37453990683048</v>
+        <v>-23.59288444896893</v>
       </c>
       <c r="F39">
-        <v>-1.001734078676713</v>
+        <v>-0.9606056371277181</v>
       </c>
       <c r="G39">
-        <v>-3.000816701674735</v>
+        <v>-3.733323754581754</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.643384335307317</v>
       </c>
       <c r="E40">
-        <v>-20.08214169040076</v>
+        <v>-24.53115718541757</v>
       </c>
       <c r="F40">
-        <v>-0.826985004851741</v>
+        <v>-0.7880119752848298</v>
       </c>
       <c r="G40">
-        <v>-2.82806634282536</v>
+        <v>-4.204069722549981</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.750597542335854</v>
       </c>
       <c r="E41">
-        <v>-19.31340304023163</v>
+        <v>-23.06919772659865</v>
       </c>
       <c r="F41">
-        <v>-1.09597660972581</v>
+        <v>-0.8227735849759084</v>
       </c>
       <c r="G41">
-        <v>-2.573362100516348</v>
+        <v>-4.133809364113941</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.875075687536377</v>
       </c>
       <c r="E42">
-        <v>-19.91672343654417</v>
+        <v>-22.23068512617239</v>
       </c>
       <c r="F42">
-        <v>-1.036677100829005</v>
+        <v>-0.8373835008590832</v>
       </c>
       <c r="G42">
-        <v>-3.068581188281671</v>
+        <v>-4.175591720550118</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.023750759967217</v>
       </c>
       <c r="E43">
-        <v>-18.61436773572708</v>
+        <v>-21.69511191299045</v>
       </c>
       <c r="F43">
-        <v>-0.8335581001929551</v>
+        <v>-0.8233849201191743</v>
       </c>
       <c r="G43">
-        <v>-3.777949211877653</v>
+        <v>-4.366758271745206</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.199535062824581</v>
       </c>
       <c r="E44">
-        <v>-18.00131221206914</v>
+        <v>-20.43036354071969</v>
       </c>
       <c r="F44">
-        <v>-1.309687115974055</v>
+        <v>-0.3037218838513493</v>
       </c>
       <c r="G44">
-        <v>-3.314092998885374</v>
+        <v>-4.763124126312616</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.40343237769735</v>
       </c>
       <c r="E45">
-        <v>-17.49180870637315</v>
+        <v>-20.04334239020422</v>
       </c>
       <c r="F45">
-        <v>-1.167749674973971</v>
+        <v>-0.4683980100582798</v>
       </c>
       <c r="G45">
-        <v>-2.90657926491391</v>
+        <v>-4.601641741118486</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.633854325461318</v>
       </c>
       <c r="E46">
-        <v>-16.7390765326499</v>
+        <v>-19.33394482344423</v>
       </c>
       <c r="F46">
-        <v>-1.227173438981196</v>
+        <v>-0.8908637287512221</v>
       </c>
       <c r="G46">
-        <v>-4.268709147881355</v>
+        <v>-4.790207990700825</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.888639535177553</v>
       </c>
       <c r="E47">
-        <v>-16.17477555673412</v>
+        <v>-18.30175136609591</v>
       </c>
       <c r="F47">
-        <v>-0.4612583114135508</v>
+        <v>-0.5341803222493942</v>
       </c>
       <c r="G47">
-        <v>-3.859336563761019</v>
+        <v>-5.013878312055274</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.162690401459932</v>
       </c>
       <c r="E48">
-        <v>-14.93980570966238</v>
+        <v>-17.03877226184953</v>
       </c>
       <c r="F48">
-        <v>-0.454626401986738</v>
+        <v>-0.5851282309911749</v>
       </c>
       <c r="G48">
-        <v>-4.694949752804875</v>
+        <v>-5.558623224714016</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.450196430171552</v>
       </c>
       <c r="E49">
-        <v>-14.75814839952571</v>
+        <v>-17.21804147547443</v>
       </c>
       <c r="F49">
-        <v>-0.5018657098661854</v>
+        <v>-0.6468531996433773</v>
       </c>
       <c r="G49">
-        <v>-3.607423207419907</v>
+        <v>-5.676427852898821</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.742038306720986</v>
       </c>
       <c r="E50">
-        <v>-12.95626105340354</v>
+        <v>-15.15917002541718</v>
       </c>
       <c r="F50">
-        <v>-0.740468656568555</v>
+        <v>-0.568803594584205</v>
       </c>
       <c r="G50">
-        <v>-3.854566733393055</v>
+        <v>-6.292683670652748</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.030434408281676</v>
       </c>
       <c r="E51">
-        <v>-13.46409496814695</v>
+        <v>-15.19987564961182</v>
       </c>
       <c r="F51">
-        <v>-0.5503790468111385</v>
+        <v>-0.6861989945415482</v>
       </c>
       <c r="G51">
-        <v>-5.37044075458657</v>
+        <v>-6.225488326366674</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.305620702597615</v>
       </c>
       <c r="E52">
-        <v>-11.80072552613047</v>
+        <v>-14.6449692377128</v>
       </c>
       <c r="F52">
-        <v>-1.190363276702995</v>
+        <v>-0.6453969297492558</v>
       </c>
       <c r="G52">
-        <v>-4.986457661614811</v>
+        <v>-5.903761048914602</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.561824238230099</v>
       </c>
       <c r="E53">
-        <v>-12.9168595375649</v>
+        <v>-14.58042002730232</v>
       </c>
       <c r="F53">
-        <v>-1.101659210109015</v>
+        <v>-0.6812536411468352</v>
       </c>
       <c r="G53">
-        <v>-5.355930236149163</v>
+        <v>-6.319524735793983</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.792899248975812</v>
       </c>
       <c r="E54">
-        <v>-9.630917648375725</v>
+        <v>-12.96835520478145</v>
       </c>
       <c r="F54">
-        <v>-1.154368227949148</v>
+        <v>-0.7581783232730056</v>
       </c>
       <c r="G54">
-        <v>-5.614318239076236</v>
+        <v>-6.155724009402945</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.999142738550377</v>
       </c>
       <c r="E55">
-        <v>-11.69745592653861</v>
+        <v>-12.70260782495097</v>
       </c>
       <c r="F55">
-        <v>-1.468695552411031</v>
+        <v>-0.377249431258639</v>
       </c>
       <c r="G55">
-        <v>-5.599175920447779</v>
+        <v>-7.062412109195269</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.179760095988156</v>
       </c>
       <c r="E56">
-        <v>-10.38286901836991</v>
+        <v>-12.02656054512935</v>
       </c>
       <c r="F56">
-        <v>-1.022344688025768</v>
+        <v>-0.8303589452833434</v>
       </c>
       <c r="G56">
-        <v>-5.372372705583994</v>
+        <v>-7.078442080984704</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.339849135465294</v>
       </c>
       <c r="E57">
-        <v>-11.14129109160817</v>
+        <v>-11.16096485365389</v>
       </c>
       <c r="F57">
-        <v>-0.5638565844546864</v>
+        <v>-0.9230673399024556</v>
       </c>
       <c r="G57">
-        <v>-5.671772895292866</v>
+        <v>-6.747425774277451</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.481058814428969</v>
       </c>
       <c r="E58">
-        <v>-10.19087851845706</v>
+        <v>-11.15356383107304</v>
       </c>
       <c r="F58">
-        <v>-0.799559416879855</v>
+        <v>-0.8145379562572757</v>
       </c>
       <c r="G58">
-        <v>-6.197198297977371</v>
+        <v>-6.798442334332396</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.60946277406871</v>
       </c>
       <c r="E59">
-        <v>-8.909147665079072</v>
+        <v>-10.48681143819639</v>
       </c>
       <c r="F59">
-        <v>-1.107866167058192</v>
+        <v>-0.8105510239476016</v>
       </c>
       <c r="G59">
-        <v>-7.413249188838255</v>
+        <v>-7.10729864095028</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.72545671736349</v>
       </c>
       <c r="E60">
-        <v>-7.977985226418539</v>
+        <v>-10.03747965817452</v>
       </c>
       <c r="F60">
-        <v>-0.9478578911660365</v>
+        <v>-1.071565450732712</v>
       </c>
       <c r="G60">
-        <v>-6.158308646548147</v>
+        <v>-7.211227161633317</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.833416800481307</v>
       </c>
       <c r="E61">
-        <v>-8.230425717164268</v>
+        <v>-9.890788234181572</v>
       </c>
       <c r="F61">
-        <v>-1.543295007237544</v>
+        <v>-1.338588026290327</v>
       </c>
       <c r="G61">
-        <v>-7.196050903325176</v>
+        <v>-7.228314484982154</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.931868136544898</v>
       </c>
       <c r="E62">
-        <v>-7.927232984029134</v>
+        <v>-9.216938003150791</v>
       </c>
       <c r="F62">
-        <v>-1.574741490582618</v>
+        <v>-0.8928899154184696</v>
       </c>
       <c r="G62">
-        <v>-6.606521277950476</v>
+        <v>-7.301639857568162</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.023733449610045</v>
       </c>
       <c r="E63">
-        <v>-7.186096576324806</v>
+        <v>-8.521648895261245</v>
       </c>
       <c r="F63">
-        <v>-1.029486043405303</v>
+        <v>-1.093926400403882</v>
       </c>
       <c r="G63">
-        <v>-6.217781408333708</v>
+        <v>-7.397357586512148</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-8.104935415070747</v>
       </c>
       <c r="E64">
-        <v>-6.844366195306589</v>
+        <v>-9.112380908048232</v>
       </c>
       <c r="F64">
-        <v>-1.787487777174004</v>
+        <v>-1.000264554904147</v>
       </c>
       <c r="G64">
-        <v>-6.357897459794167</v>
+        <v>-7.270454513427313</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-8.17513129471198</v>
       </c>
       <c r="E65">
-        <v>-5.093027584218914</v>
+        <v>-8.592091512541662</v>
       </c>
       <c r="F65">
-        <v>-1.612911832136217</v>
+        <v>-0.8851927255116566</v>
       </c>
       <c r="G65">
-        <v>-6.738303832676102</v>
+        <v>-7.520237502182077</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-8.226997385844307</v>
       </c>
       <c r="E66">
-        <v>-6.113691726929503</v>
+        <v>-8.56886675481322</v>
       </c>
       <c r="F66">
-        <v>-2.101802676124846</v>
+        <v>-1.116516807845627</v>
       </c>
       <c r="G66">
-        <v>-6.23485828870418</v>
+        <v>-7.443954155974338</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.258770800672579</v>
       </c>
       <c r="E67">
-        <v>-6.885242101165551</v>
+        <v>-8.200165419451567</v>
       </c>
       <c r="F67">
-        <v>-1.739319041068616</v>
+        <v>-1.202682756717429</v>
       </c>
       <c r="G67">
-        <v>-6.129835866037466</v>
+        <v>-7.580754561804083</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.262731244909988</v>
       </c>
       <c r="E68">
-        <v>-6.088203469029031</v>
+        <v>-7.899560136971802</v>
       </c>
       <c r="F68">
-        <v>-1.628086694588101</v>
+        <v>-1.372751554716584</v>
       </c>
       <c r="G68">
-        <v>-6.082411690539892</v>
+        <v>-7.695684760194072</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.238412945093543</v>
       </c>
       <c r="E69">
-        <v>-6.864995195957012</v>
+        <v>-7.13476703756125</v>
       </c>
       <c r="F69">
-        <v>-1.963799151920657</v>
+        <v>-1.246684804786736</v>
       </c>
       <c r="G69">
-        <v>-7.285596832055771</v>
+        <v>-7.748156810358562</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.180103923054299</v>
       </c>
       <c r="E70">
-        <v>-5.371205525544606</v>
+        <v>-7.426862390036441</v>
       </c>
       <c r="F70">
-        <v>-2.035824040859268</v>
+        <v>-1.353638633631791</v>
       </c>
       <c r="G70">
-        <v>-6.474519420679197</v>
+        <v>-7.511823072364919</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.090893435734293</v>
       </c>
       <c r="E71">
-        <v>-5.849688695855452</v>
+        <v>-6.96361735207639</v>
       </c>
       <c r="F71">
-        <v>-1.435890546525365</v>
+        <v>-1.509336085559778</v>
       </c>
       <c r="G71">
-        <v>-5.662321999873036</v>
+        <v>-7.43671195047859</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.969170401478251</v>
       </c>
       <c r="E72">
-        <v>-5.991986022266728</v>
+        <v>-7.300646297874902</v>
       </c>
       <c r="F72">
-        <v>-1.583352369734719</v>
+        <v>-1.645358983303873</v>
       </c>
       <c r="G72">
-        <v>-6.471224661005212</v>
+        <v>-7.349176295083153</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.822536587608225</v>
       </c>
       <c r="E73">
-        <v>-6.161960348946661</v>
+        <v>-7.930426803537928</v>
       </c>
       <c r="F73">
-        <v>-1.172186410783365</v>
+        <v>-1.473164594549135</v>
       </c>
       <c r="G73">
-        <v>-6.770316782852333</v>
+        <v>-7.315484636134835</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.652562577825146</v>
       </c>
       <c r="E74">
-        <v>-5.576922388886013</v>
+        <v>-7.869179396130681</v>
       </c>
       <c r="F74">
-        <v>-2.231316262817743</v>
+        <v>-1.455836805217374</v>
       </c>
       <c r="G74">
-        <v>-6.355009976276396</v>
+        <v>-6.899391995436973</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.469035878094222</v>
       </c>
       <c r="E75">
-        <v>-8.368129591850282</v>
+        <v>-7.91983196144829</v>
       </c>
       <c r="F75">
-        <v>-1.990263833705295</v>
+        <v>-1.487816757169852</v>
       </c>
       <c r="G75">
-        <v>-6.202670418640344</v>
+        <v>-6.545991164605514</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.274120613236058</v>
       </c>
       <c r="E76">
-        <v>-8.32118999745707</v>
+        <v>-8.265636642776164</v>
       </c>
       <c r="F76">
-        <v>-2.547913313963297</v>
+        <v>-1.554859844548027</v>
       </c>
       <c r="G76">
-        <v>-5.166899274029606</v>
+        <v>-6.982056001425393</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.077364601041689</v>
       </c>
       <c r="E77">
-        <v>-4.994600629031803</v>
+        <v>-9.10166146961885</v>
       </c>
       <c r="F77">
-        <v>-1.63045665372751</v>
+        <v>-1.626829232870651</v>
       </c>
       <c r="G77">
-        <v>-5.043742619433019</v>
+        <v>-6.261453943853851</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-6.879317888289885</v>
       </c>
       <c r="E78">
-        <v>-8.727664789818039</v>
+        <v>-9.153036693706978</v>
       </c>
       <c r="F78">
-        <v>-2.088448565224315</v>
+        <v>-1.777747004884485</v>
       </c>
       <c r="G78">
-        <v>-4.68497148697764</v>
+        <v>-5.580227136205479</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.687251699817119</v>
       </c>
       <c r="E79">
-        <v>-8.765832801893215</v>
+        <v>-9.41365901076262</v>
       </c>
       <c r="F79">
-        <v>-2.528281834884352</v>
+        <v>-2.038121103667231</v>
       </c>
       <c r="G79">
-        <v>-4.745689573933162</v>
+        <v>-5.471549671111206</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.498019445012082</v>
       </c>
       <c r="E80">
-        <v>-8.466186911229485</v>
+        <v>-9.994834484291177</v>
       </c>
       <c r="F80">
-        <v>-1.858956003217934</v>
+        <v>-1.479263035368545</v>
       </c>
       <c r="G80">
-        <v>-5.138037492574848</v>
+        <v>-4.963595371230432</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.315341839147374</v>
       </c>
       <c r="E81">
-        <v>-10.13427024809964</v>
+        <v>-10.59421763626778</v>
       </c>
       <c r="F81">
-        <v>-2.34635744261633</v>
+        <v>-1.54326435764364</v>
       </c>
       <c r="G81">
-        <v>-4.846683617695787</v>
+        <v>-5.824491010894629</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.132899075340621</v>
       </c>
       <c r="E82">
-        <v>-9.494663244442075</v>
+        <v>-10.80991466642275</v>
       </c>
       <c r="F82">
-        <v>-2.071177933243348</v>
+        <v>-1.735878002877387</v>
       </c>
       <c r="G82">
-        <v>-4.249640269387864</v>
+        <v>-4.828416237791768</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.95208627230036</v>
       </c>
       <c r="E83">
-        <v>-11.51476446678205</v>
+        <v>-11.70912645036138</v>
       </c>
       <c r="F83">
-        <v>-1.650803842242474</v>
+        <v>-1.594955311945732</v>
       </c>
       <c r="G83">
-        <v>-4.203688553839679</v>
+        <v>-4.662558244662932</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.765053876223348</v>
       </c>
       <c r="E84">
-        <v>-12.55473273573045</v>
+        <v>-12.12496258104851</v>
       </c>
       <c r="F84">
-        <v>-2.230675934815379</v>
+        <v>-1.843176432562007</v>
       </c>
       <c r="G84">
-        <v>-3.596969786077089</v>
+        <v>-4.469300487050362</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.573086125178276</v>
       </c>
       <c r="E85">
-        <v>-14.41171658328778</v>
+        <v>-13.35881521427387</v>
       </c>
       <c r="F85">
-        <v>-2.166144457402492</v>
+        <v>-1.606188802295096</v>
       </c>
       <c r="G85">
-        <v>-3.916099372661004</v>
+        <v>-4.323996886087361</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.36911469620143</v>
       </c>
       <c r="E86">
-        <v>-16.09395821756429</v>
+        <v>-14.28736528301109</v>
       </c>
       <c r="F86">
-        <v>-2.441878972935349</v>
+        <v>-1.865454545492896</v>
       </c>
       <c r="G86">
-        <v>-3.94800789305359</v>
+        <v>-3.493503367186678</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-5.15785664014619</v>
       </c>
       <c r="E87">
-        <v>-14.22455211493438</v>
+        <v>-15.70675017253919</v>
       </c>
       <c r="F87">
-        <v>-2.042974508280233</v>
+        <v>-1.80429949361382</v>
       </c>
       <c r="G87">
-        <v>-3.510825657548715</v>
+        <v>-3.834926101834109</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.936842877514808</v>
       </c>
       <c r="E88">
-        <v>-17.79264656868711</v>
+        <v>-16.79265295874019</v>
       </c>
       <c r="F88">
-        <v>-1.674508403840985</v>
+        <v>-2.280115386516662</v>
       </c>
       <c r="G88">
-        <v>-2.937239849391944</v>
+        <v>-3.745048608540444</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.717623125451547</v>
       </c>
       <c r="E89">
-        <v>-18.83513999012099</v>
+        <v>-17.59978804760737</v>
       </c>
       <c r="F89">
-        <v>-1.711506605519622</v>
+        <v>-2.05585976323078</v>
       </c>
       <c r="G89">
-        <v>-3.715651624444508</v>
+        <v>-3.572572377873136</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.50431169516636</v>
       </c>
       <c r="E90">
-        <v>-19.25015378496581</v>
+        <v>-19.51382040592255</v>
       </c>
       <c r="F90">
-        <v>-1.671189135657968</v>
+        <v>-1.814156237339732</v>
       </c>
       <c r="G90">
-        <v>-2.897154476939991</v>
+        <v>-3.946582426506843</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.314068013920487</v>
       </c>
       <c r="E91">
-        <v>-20.90032847460331</v>
+        <v>-20.54484681088859</v>
       </c>
       <c r="F91">
-        <v>-2.340448697932161</v>
+        <v>-1.830210825973389</v>
       </c>
       <c r="G91">
-        <v>-2.768209801584906</v>
+        <v>-3.923607874105046</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.152930700642624</v>
       </c>
       <c r="E92">
-        <v>-24.01949816304399</v>
+        <v>-22.3618144673312</v>
       </c>
       <c r="F92">
-        <v>-2.00270177025833</v>
+        <v>-1.757037819814497</v>
       </c>
       <c r="G92">
-        <v>-3.713025215385848</v>
+        <v>-3.915820022989755</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.036814338742102</v>
       </c>
       <c r="E93">
-        <v>-24.98791075407691</v>
+        <v>-24.71123212203949</v>
       </c>
       <c r="F93">
-        <v>-1.973091777445261</v>
+        <v>-1.900542531940678</v>
       </c>
       <c r="G93">
-        <v>-2.823069377677969</v>
+        <v>-4.276805066858397</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.965986693646389</v>
       </c>
       <c r="E94">
-        <v>-28.20532257980075</v>
+        <v>-26.21045003965344</v>
       </c>
       <c r="F94">
-        <v>-2.328989063281833</v>
+        <v>-1.876226635198901</v>
       </c>
       <c r="G94">
-        <v>-4.347101975718714</v>
+        <v>-4.442780543493834</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.948493658821035</v>
       </c>
       <c r="E95">
-        <v>-29.90847563309776</v>
+        <v>-27.79460528207147</v>
       </c>
       <c r="F95">
-        <v>-1.563371319611792</v>
+        <v>-2.082683956468233</v>
       </c>
       <c r="G95">
-        <v>-3.304485458790077</v>
+        <v>-4.321153785227639</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.972841802179132</v>
       </c>
       <c r="E96">
-        <v>-30.64341752611111</v>
+        <v>-30.83993917957935</v>
       </c>
       <c r="F96">
-        <v>-2.12832534362768</v>
+        <v>-1.517787089803138</v>
       </c>
       <c r="G96">
-        <v>-4.297860721985726</v>
+        <v>-4.812005097292031</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.036378184759312</v>
       </c>
       <c r="E97">
-        <v>-33.7144805677763</v>
+        <v>-32.59244068983797</v>
       </c>
       <c r="F97">
-        <v>-2.484172927420083</v>
+        <v>-2.218206520301038</v>
       </c>
       <c r="G97">
-        <v>-5.202890998962694</v>
+        <v>-4.547782080203819</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.112574578237479</v>
       </c>
       <c r="E98">
-        <v>-36.11297256749876</v>
+        <v>-34.22682279341281</v>
       </c>
       <c r="F98">
-        <v>-2.04893875358039</v>
+        <v>-2.225602184473232</v>
       </c>
       <c r="G98">
-        <v>-4.303105707869273</v>
+        <v>-4.675533645280765</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.190395714190968</v>
       </c>
       <c r="E99">
-        <v>-37.71716290134776</v>
+        <v>-35.96053517563792</v>
       </c>
       <c r="F99">
-        <v>-2.024650192962905</v>
+        <v>-2.348853313600965</v>
       </c>
       <c r="G99">
-        <v>-5.079499377352906</v>
+        <v>-4.831167962590802</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.230292800564311</v>
       </c>
       <c r="E100">
-        <v>-40.60771699580759</v>
+        <v>-38.32847199964361</v>
       </c>
       <c r="F100">
-        <v>-2.071429756933799</v>
+        <v>-2.312726554430073</v>
       </c>
       <c r="G100">
-        <v>-4.705439724571968</v>
+        <v>-4.528337254489207</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.22791447807091</v>
       </c>
       <c r="E101">
-        <v>-41.72444699306713</v>
+        <v>-41.06078458941614</v>
       </c>
       <c r="F101">
-        <v>-2.292825027577814</v>
+        <v>-2.160360796196146</v>
       </c>
       <c r="G101">
-        <v>-4.699609931900012</v>
+        <v>-5.114478133384642</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.133325260687301</v>
       </c>
       <c r="E102">
-        <v>-42.94762379658201</v>
+        <v>-43.18142052169059</v>
       </c>
       <c r="F102">
-        <v>-2.043708441799114</v>
+        <v>-1.898145236676976</v>
       </c>
       <c r="G102">
-        <v>-4.339136593971228</v>
+        <v>-5.58524759805419</v>
       </c>
     </row>
   </sheetData>
